--- a/Monthly_Budget_Planner.xlsx
+++ b/Monthly_Budget_Planner.xlsx
@@ -22,13 +22,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
-    <t xml:space="preserve">MY MONTHLY BUDGET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple personal budget. Fill in the blue cells. Totals calculate for you.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Month:</t>
+    <t xml:space="preserve">MONTHLY BUDGET PLANNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take control of your money each month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTH</t>
   </si>
   <si>
     <t xml:space="preserve">[Enter Month]</t>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Grant / SASSA</t>
   </si>
   <si>
-    <t xml:space="preserve">Extra Income</t>
+    <t xml:space="preserve">Side Income</t>
   </si>
   <si>
     <t xml:space="preserve">Other</t>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">[Add source]</t>
   </si>
   <si>
-    <t xml:space="preserve">  TOTAL MONEY IN</t>
+    <t xml:space="preserve">  TOTAL IN</t>
   </si>
   <si>
     <t xml:space="preserve">  MONEY OUT</t>
@@ -88,13 +88,13 @@
     <t xml:space="preserve">[Add expense]</t>
   </si>
   <si>
-    <t xml:space="preserve">  TOTAL MONEY OUT</t>
+    <t xml:space="preserve">  TOTAL OUT</t>
   </si>
   <si>
     <t xml:space="preserve">  MONEY LEFT</t>
   </si>
   <si>
-    <t xml:space="preserve">Goal: Keep some money left every month for savings and emergencies.</t>
+    <t xml:space="preserve">Aim to keep money left for savings &amp; emergencies.</t>
   </si>
 </sst>
 </file>
@@ -106,7 +106,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,82 +130,75 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
-      <sz val="20"/>
-      <color rgb="FF7C3AED"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
+      <sz val="18"/>
+      <color rgb="FF1C1A17"/>
+      <name val="Georgia"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
       <sz val="10"/>
-      <color rgb="FF64748B"/>
-      <name val="Arial"/>
+      <color rgb="FF9C9280"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1E293B"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF2563EB"/>
-      <name val="Arial"/>
+      <sz val="8"/>
+      <color rgb="FF9C9280"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1C1A17"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <color rgb="FF9C9280"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF64748B"/>
-      <name val="Arial"/>
+      <color rgb="FFE8CE93"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF9C9280"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,20 +207,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF16A34A"/>
+        <fgColor rgb="FF15141F"/>
+        <bgColor rgb="FF1C1A17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B6E4F"/>
         <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
-        <bgColor rgb="FF993300"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF7F3EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="FFF7F3EA"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9E1B32"/>
+        <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
   </fills>
@@ -241,16 +246,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFDCCFAF"/>
       </left>
       <right style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFDCCFAF"/>
       </right>
       <top style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFDCCFAF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFDCCFAF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -280,20 +285,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -301,20 +314,52 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -325,27 +370,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -362,7 +387,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFDC2626"/>
+      <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -373,17 +398,17 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF0B6E4F"/>
+      <rgbColor rgb="FFDCCFAF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF7C3AED"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFF7F3EA"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCBD5E1"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -399,23 +424,23 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF2563EB"/>
+      <rgbColor rgb="FFE8CE93"/>
+      <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF64748B"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF9C9280"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF16A34A"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF15141F"/>
+      <rgbColor rgb="FF1C1A17"/>
+      <rgbColor rgb="FF9E1B32"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1E293B"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -601,185 +626,242 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="2.5"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="10" t="n">
-        <f aca="false">SUM(C8:C12)</f>
+      <c r="C14" s="15" t="n">
+        <f aca="false">SUM(C9:C13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="7"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="8" t="s">
+      <c r="C26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="12" t="s">
+      <c r="C27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="13" t="n">
-        <f aca="false">SUM(C16:C26)</f>
+      <c r="C28" s="18" t="n">
+        <f aca="false">SUM(C17:C27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="15" t="n">
-        <f aca="false">C13-C27</f>
+      <c r="C30" s="20" t="n">
+        <f aca="false">C14-C28</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16" t="s">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="21" t="s">
         <v>24</v>
       </c>
+      <c r="C32" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
